--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/27,07,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/27,07,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\07,26\27,07,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C809EB20-C2D6-42B1-8057-C17728783F07}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA38BFB-A967-4593-9437-38236C49457D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
